--- a/docs/pension_data_combined_2026-10-15.xlsx
+++ b/docs/pension_data_combined_2026-10-15.xlsx
@@ -1224,9 +1224,6 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="C48" t="n">
-        <v>1.19</v>
-      </c>
       <c r="D48" t="n">
         <v>4078162.45</v>
       </c>

--- a/docs/pension_data_combined_2026-10-15.xlsx
+++ b/docs/pension_data_combined_2026-10-15.xlsx
@@ -1224,6 +1224,9 @@
           <t>2026-10-15</t>
         </is>
       </c>
+      <c r="C48" t="n">
+        <v>1.19</v>
+      </c>
       <c r="D48" t="n">
         <v>4078162.45</v>
       </c>
